--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_GiaThanh_050826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_GiaThanh_050826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09C2C8A-6076-4F1D-93D6-C61BFE1F22FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2732991C-EAE9-47A2-8238-39434DC001AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>00BD000CC2</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Khách đã đồng ý báo giá sửa chữa công nợ ghi KD. Lực</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1132,9 @@
       <c r="J10" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="33"/>
+      <c r="K10" s="33" t="s">
+        <v>32</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1161,7 +1169,9 @@
         <f t="shared" ref="J11" si="0">SUM(H11*I11)</f>
         <v>150000</v>
       </c>
-      <c r="K11" s="33"/>
+      <c r="K11" s="33" t="s">
+        <v>33</v>
+      </c>
       <c r="AA11" s="32"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
